--- a/data/raw/sales/Week 29/Tonor/Vendor Sales (SP-API).xlsx
+++ b/data/raw/sales/Week 29/Tonor/Vendor Sales (SP-API).xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,82 +417,82 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ASIN</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>SKU</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Brand</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Model</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>category_l0</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>category_l1</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>category_l2</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Qty</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Sale</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>ShippedUnits</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>ShippedRevenue</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>CustomerReturns</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Channel</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Week</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>WindowStart</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>WindowEnd</t>
         </is>
@@ -543,19 +531,19 @@
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I2" t="n">
-        <v>43655.04</v>
+        <v>45298.26</v>
       </c>
       <c r="J2" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -572,7 +560,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
@@ -609,10 +597,10 @@
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>2202.54</v>
       </c>
       <c r="J3" t="n">
         <v>2</v>
@@ -638,7 +626,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
@@ -675,19 +663,19 @@
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I4" t="n">
-        <v>29734.72</v>
+        <v>32022.01</v>
       </c>
       <c r="J4" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -704,7 +692,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
@@ -770,7 +758,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
@@ -807,10 +795,10 @@
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I6" t="n">
-        <v>8470.33</v>
+        <v>13552.53</v>
       </c>
       <c r="J6" t="n">
         <v>6</v>
@@ -836,7 +824,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
@@ -873,13 +861,13 @@
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
+        <v>12</v>
+      </c>
+      <c r="I7" t="n">
+        <v>22362.72</v>
+      </c>
+      <c r="J7" t="n">
         <v>11</v>
-      </c>
-      <c r="I7" t="n">
-        <v>20499.16</v>
-      </c>
-      <c r="J7" t="n">
-        <v>9</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -902,7 +890,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
@@ -939,10 +927,10 @@
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I8" t="n">
-        <v>20332.22</v>
+        <v>25415.28</v>
       </c>
       <c r="J8" t="n">
         <v>10</v>
@@ -968,7 +956,7 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
@@ -1034,7 +1022,7 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
@@ -1100,7 +1088,7 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1131,7 @@
         <v>2372.03</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -1166,7 +1154,7 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
@@ -1209,7 +1197,7 @@
         <v>3388.98</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
@@ -1232,7 +1220,7 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
@@ -1298,7 +1286,7 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
@@ -1335,13 +1323,13 @@
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I14" t="n">
-        <v>21345.8</v>
+        <v>23124.61</v>
       </c>
       <c r="J14" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -1364,7 +1352,7 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
@@ -1430,7 +1418,7 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
@@ -1496,7 +1484,7 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
@@ -1562,7 +1550,7 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
@@ -1605,7 +1593,7 @@
         <v>9317.799999999999</v>
       </c>
       <c r="J18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -1628,7 +1616,7 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
@@ -1665,19 +1653,19 @@
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I19" t="n">
-        <v>18634.72</v>
+        <v>20328.78</v>
       </c>
       <c r="J19" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -1694,7 +1682,7 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
@@ -1760,7 +1748,7 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
